--- a/data/trans_dic/P38C-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Clase-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,3; 89,18</t>
+          <t>82,02; 89,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,44; 88,62</t>
+          <t>81,98; 88,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,24; 94,01</t>
+          <t>88,26; 94,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85,94; 91,58</t>
+          <t>86,37; 91,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,68; 90,53</t>
+          <t>85,56; 90,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,5; 89,48</t>
+          <t>84,55; 89,32</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,34; 89,27</t>
+          <t>81,8; 89,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,48; 88,73</t>
+          <t>81,49; 89,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,6; 91,45</t>
+          <t>84,42; 91,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,29; 90,71</t>
+          <t>84,09; 90,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,57; 89,43</t>
+          <t>84,54; 89,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,87; 88,77</t>
+          <t>83,66; 88,82</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,15; 89,22</t>
+          <t>82,96; 89,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,92; 87,81</t>
+          <t>22,53; 87,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,2; 93,19</t>
+          <t>82,03; 92,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,93; 94,86</t>
+          <t>87,32; 94,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,97; 88,95</t>
+          <t>84,29; 89,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,82; 89,16</t>
+          <t>29,85; 89,04</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,26; 85,7</t>
+          <t>81,37; 85,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,35; 84,12</t>
+          <t>78,27; 84,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,23; 88,07</t>
+          <t>83,28; 88,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,72; 95,3</t>
+          <t>87,91; 95,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,07; 86,23</t>
+          <t>82,72; 86,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,61; 90,57</t>
+          <t>83,46; 90,18</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,84; 83,41</t>
+          <t>76,61; 83,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>74,73; 83,45</t>
+          <t>74,35; 83,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,21; 89,2</t>
+          <t>84,22; 89,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,76; 90,09</t>
+          <t>60,28; 90,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,69; 85,75</t>
+          <t>81,65; 85,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,94; 86,18</t>
+          <t>66,9; 85,98</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,31; 60,62</t>
+          <t>48,43; 60,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,34; 57,82</t>
+          <t>36,27; 57,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85,05; 89,19</t>
+          <t>84,97; 89,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78,82; 84,71</t>
+          <t>78,85; 85,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78,06; 82,54</t>
+          <t>78,18; 82,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,61; 77,26</t>
+          <t>69,51; 77,27</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>80,29; 83,03</t>
+          <t>79,86; 82,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>56,56; 80,85</t>
+          <t>59,53; 80,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,29; 88,53</t>
+          <t>86,24; 88,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,25; 88,96</t>
+          <t>80,26; 88,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,66; 85,48</t>
+          <t>83,68; 85,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,55; 84,21</t>
+          <t>70,18; 84,22</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>352370; 381816</t>
+          <t>351150; 382050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>410248; 446389</t>
+          <t>412932; 448006</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305330; 325315</t>
+          <t>305412; 326018</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>384563; 409807</t>
+          <t>386498; 411142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>663314; 700866</t>
+          <t>662345; 701593</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>803753; 851166</t>
+          <t>804263; 849572</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>307101; 332954</t>
+          <t>305071; 333009</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368464; 401254</t>
+          <t>368514; 402884</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>313232; 338606</t>
+          <t>312561; 337169</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>322474; 347057</t>
+          <t>321712; 346549</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>628533; 664699</t>
+          <t>628353; 664729</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>700145; 741018</t>
+          <t>698396; 741492</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>430644; 462073</t>
+          <t>429673; 463031</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133097; 586820</t>
+          <t>150574; 587929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135829; 153995</t>
+          <t>135562; 152711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145088; 158327</t>
+          <t>145753; 158488</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>573654; 607702</t>
+          <t>575830; 609912</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>224009; 744628</t>
+          <t>249305; 743601</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>925410; 975922</t>
+          <t>926658; 977056</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>800453; 870476</t>
+          <t>810001; 875379</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>683563; 723364</t>
+          <t>683979; 722971</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>857249; 931309</t>
+          <t>859097; 936579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1628349; 1690310</t>
+          <t>1621371; 1686773</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1682196; 1822301</t>
+          <t>1679269; 1814342</t>
         </is>
       </c>
     </row>
@@ -1816,32 +1816,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>471830; 512133</t>
+          <t>470363; 511014</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>355020; 396404</t>
+          <t>353204; 395886</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>619813; 656573</t>
+          <t>619951; 657448</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>502773; 757938</t>
+          <t>507120; 758360</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1102855; 1157693</t>
+          <t>1102346; 1159521</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>881178; 1134465</t>
+          <t>880685; 1131878</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>134812; 169166</t>
+          <t>135131; 168338</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>84997; 139062</t>
+          <t>87236; 137775</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>915009; 959644</t>
+          <t>914211; 958586</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>594970; 639416</t>
+          <t>595214; 641703</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1057644; 1118421</t>
+          <t>1059253; 1117389</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>692861; 769046</t>
+          <t>691850; 769135</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2690418; 2782071</t>
+          <t>2675861; 2773495</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1908693; 2728217</t>
+          <t>2008970; 2731808</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3033117; 3111830</t>
+          <t>3031334; 3108091</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2865109; 3176235</t>
+          <t>2865694; 3170299</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5743896; 5868590</t>
+          <t>5745254; 5863310</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4760658; 5847988</t>
+          <t>4874061; 5848888</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38C-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Clase-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,19%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,02; 89,24</t>
+          <t>82,39; 89,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,98; 88,94</t>
+          <t>81,64; 88,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88,26; 94,22</t>
+          <t>88,38; 94,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86,37; 91,88</t>
+          <t>85,76; 91,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,56; 90,63</t>
+          <t>85,96; 90,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,55; 89,32</t>
+          <t>84,74; 89,41</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,08%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>81,8; 89,29</t>
+          <t>81,6; 89,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81,49; 89,09</t>
+          <t>81,14; 88,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,42; 91,06</t>
+          <t>84,44; 91,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,09; 90,58</t>
+          <t>84,1; 90,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,54; 89,44</t>
+          <t>84,21; 89,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,66; 88,82</t>
+          <t>83,47; 88,52</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,96; 89,4</t>
+          <t>83,13; 89,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,53; 87,98</t>
+          <t>81,91; 89,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,03; 92,41</t>
+          <t>82,22; 92,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,32; 94,95</t>
+          <t>86,8; 94,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,29; 89,28</t>
+          <t>84,03; 89,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>29,85; 89,04</t>
+          <t>84,23; 89,85</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81,37; 85,8</t>
+          <t>81,55; 85,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,27; 84,59</t>
+          <t>78,32; 84,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,28; 88,03</t>
+          <t>83,23; 88,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87,91; 95,84</t>
+          <t>86,46; 90,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,72; 86,05</t>
+          <t>82,88; 86,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,46; 90,18</t>
+          <t>82,39; 86,09</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,61; 83,23</t>
+          <t>76,94; 83,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>74,35; 83,34</t>
+          <t>70,7; 79,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,22; 89,32</t>
+          <t>84,15; 89,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,28; 90,14</t>
+          <t>86,4; 90,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,65; 85,89</t>
+          <t>81,63; 85,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,9; 85,98</t>
+          <t>80,85; 85,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,43; 60,33</t>
+          <t>48,01; 60,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36,27; 57,29</t>
+          <t>32,61; 52,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>84,97; 89,1</t>
+          <t>84,84; 89,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78,85; 85,01</t>
+          <t>76,94; 83,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78,18; 82,47</t>
+          <t>78,32; 82,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,51; 77,27</t>
+          <t>67,98; 75,44</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>83,11%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>79,86; 82,77</t>
+          <t>80,22; 82,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59,53; 80,95</t>
+          <t>77,69; 80,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,24; 88,43</t>
+          <t>86,27; 88,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,26; 88,8</t>
+          <t>85,55; 87,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>83,68; 85,4</t>
+          <t>83,71; 85,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,18; 84,22</t>
+          <t>82,03; 84,14</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>431484</t>
+          <t>470090</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399156</t>
+          <t>434630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>830640</t>
+          <t>904720</t>
         </is>
       </c>
     </row>
@@ -1344,32 +1344,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>351150; 382050</t>
+          <t>352753; 382010</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>412932; 448006</t>
+          <t>448359; 487526</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305412; 326018</t>
+          <t>305804; 326162</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>386498; 411142</t>
+          <t>418838; 447161</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>662345; 701593</t>
+          <t>665492; 702453</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>804263; 849572</t>
+          <t>879260; 927722</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>386054</t>
+          <t>410314</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335302</t>
+          <t>369856</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>721356</t>
+          <t>780170</t>
         </is>
       </c>
     </row>
@@ -1462,32 +1462,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>305071; 333009</t>
+          <t>304353; 333806</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>368514; 402884</t>
+          <t>392083; 427530</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>312561; 337169</t>
+          <t>312641; 337342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>321712; 346549</t>
+          <t>355872; 382460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>628353; 664729</t>
+          <t>625862; 665115</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>698396; 741492</t>
+          <t>756503; 802279</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>368044</t>
+          <t>403723</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153155</t>
+          <t>171178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>521199</t>
+          <t>574901</t>
         </is>
       </c>
     </row>
@@ -1580,32 +1580,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>429673; 463031</t>
+          <t>430537; 462427</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>150574; 587929</t>
+          <t>386312; 421328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135562; 152711</t>
+          <t>135874; 153186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145753; 158488</t>
+          <t>162742; 177443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>575830; 609912</t>
+          <t>574065; 609482</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>249305; 743601</t>
+          <t>555150; 592235</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>842394</t>
+          <t>918948</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>889115</t>
+          <t>760112</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1731508</t>
+          <t>1679060</t>
         </is>
       </c>
     </row>
@@ -1698,32 +1698,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>926658; 977056</t>
+          <t>928727; 977309</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>810001; 875379</t>
+          <t>886406; 951087</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>683979; 722971</t>
+          <t>683604; 723524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>859097; 936579</t>
+          <t>741909; 776473</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1621371; 1686773</t>
+          <t>1624604; 1688767</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1679269; 1814342</t>
+          <t>1639454; 1713197</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>376269</t>
+          <t>428018</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>688646</t>
+          <t>735942</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1064915</t>
+          <t>1163960</t>
         </is>
       </c>
     </row>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>470363; 511014</t>
+          <t>472391; 510968</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>353204; 395886</t>
+          <t>401528; 450083</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>619951; 657448</t>
+          <t>619373; 658054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>507120; 758360</t>
+          <t>717891; 750678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1102346; 1159521</t>
+          <t>1102000; 1156689</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>880685; 1131878</t>
+          <t>1130901; 1190767</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>111974</t>
+          <t>99222</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>619465</t>
+          <t>670668</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>731439</t>
+          <t>769890</t>
         </is>
       </c>
     </row>
@@ -1934,32 +1934,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>135131; 168338</t>
+          <t>133968; 168512</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87236; 137775</t>
+          <t>77352; 123725</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>914211; 958586</t>
+          <t>912811; 959756</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>595214; 641703</t>
+          <t>644196; 698911</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1059253; 1117389</t>
+          <t>1061254; 1116929</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>691850; 769135</t>
+          <t>730414; 810619</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2516218</t>
+          <t>2730314</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3084839</t>
+          <t>3142386</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5601057</t>
+          <t>5872700</t>
         </is>
       </c>
     </row>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2675861; 2773495</t>
+          <t>2688182; 2777208</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2008970; 2731808</t>
+          <t>2673220; 2786517</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3031334; 3108091</t>
+          <t>3032084; 3114129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2865694; 3170299</t>
+          <t>3101417; 3187392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5745254; 5863310</t>
+          <t>5747126; 5863247</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4874061; 5848888</t>
+          <t>5796328; 5945707</t>
         </is>
       </c>
     </row>
